--- a/KI_Orders_with_Summary_Updated (5).xlsx
+++ b/KI_Orders_with_Summary_Updated (5).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hassan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D6FF77-F54F-49E2-8E16-010336204C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAAD7FED-EC90-435B-B3A1-B029358BB5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="229">
   <si>
     <t>SL No.</t>
   </si>
@@ -615,9 +615,6 @@
     <t>I-153997754-9021</t>
   </si>
   <si>
-    <t>I-155312328-4448</t>
-  </si>
-  <si>
     <t>NOURNET ISP 1 - NOURNET ISP</t>
   </si>
   <si>
@@ -633,94 +630,145 @@
     <t>KIC-021-MW-MEL-STC</t>
   </si>
   <si>
-    <t>KIC-022-MW-MEL-STC</t>
+    <t>1001274298017324</t>
+  </si>
+  <si>
+    <t>QASSIM-RIYADH W-PLL66095</t>
+  </si>
+  <si>
+    <t>I-155754471-6042</t>
+  </si>
+  <si>
+    <t>10MBPS</t>
+  </si>
+  <si>
+    <t>EATC - EATC</t>
+  </si>
+  <si>
+    <t>Saleh Aljari-- 0553612927</t>
+  </si>
+  <si>
+    <t>SDH 689-11-200-01</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Pole</t>
+  </si>
+  <si>
+    <t>Invoice</t>
+  </si>
+  <si>
+    <t>Issued</t>
+  </si>
+  <si>
+    <t>Al Rajhi bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0567878430 Yahya</t>
+  </si>
+  <si>
+    <t>C0487</t>
+  </si>
+  <si>
+    <t>ZAK001 Re Routed</t>
+  </si>
+  <si>
+    <t>RIYADh</t>
+  </si>
+  <si>
+    <t>DIA-Circuit	1-274518091680</t>
+  </si>
+  <si>
+    <t>1001274526958901</t>
+  </si>
+  <si>
+    <t>Technology Equipment Trading Company	مؤسسة معدات التقانة للتجارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Mwafaq - 0568007928 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4Mbps	</t>
+  </si>
+  <si>
+    <t>As per customer hold this request he will tell us once site is ready</t>
+  </si>
+  <si>
+    <t>CE1553</t>
+  </si>
+  <si>
+    <t>Installtion is completed at both ends / pending due to alignment issue</t>
+  </si>
+  <si>
+    <t>Re Routed to ZAK001 due to ZAKA013 tower will be dismental</t>
+  </si>
+  <si>
+    <t>KIC-022-MW-MEL-Mobily</t>
+  </si>
+  <si>
+    <t>RIYADHDISTRICTS-JEDDAH W-PLL62518</t>
+  </si>
+  <si>
+    <t>RIYADHDISTRICTS-JEDDAH W-PLL62968</t>
+  </si>
+  <si>
+    <t>Z62008-Z62007-ZTE-MW-Repeater-link-16455450</t>
+  </si>
+  <si>
+    <t>Z62007-ZRS966-ZTE-MW-Repeater-link-16455452</t>
+  </si>
+  <si>
+    <t>Z62008</t>
+  </si>
+  <si>
+    <t>Colocated</t>
+  </si>
+  <si>
+    <t>Z62007</t>
+  </si>
+  <si>
+    <t>ZRS966</t>
+  </si>
+  <si>
+    <t>34Mbps</t>
+  </si>
+  <si>
+    <t>14Mbps</t>
+  </si>
+  <si>
+    <t>Zain - Zain - Id : 2-3699763</t>
+  </si>
+  <si>
+    <t>Ahmed Mahmoud Abouelnasr-- 0592444566</t>
+  </si>
+  <si>
+    <t>I-150824560-5646</t>
+  </si>
+  <si>
+    <t>I-151806701-8883</t>
+  </si>
+  <si>
+    <t>MWO-15247</t>
+  </si>
+  <si>
+    <t>MWO-15248</t>
   </si>
   <si>
     <t>KIC-023-MW-MEL-STC</t>
   </si>
   <si>
-    <t>1001274298017324</t>
-  </si>
-  <si>
-    <t>QASSIM-RIYADH W-PLL66095</t>
-  </si>
-  <si>
-    <t>I-155754471-6042</t>
-  </si>
-  <si>
-    <t>10MBPS</t>
-  </si>
-  <si>
-    <t>EATC - EATC</t>
-  </si>
-  <si>
-    <t>Saleh Aljari-- 0553612927</t>
-  </si>
-  <si>
-    <t>SDH 689-11-200-01</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Pole</t>
-  </si>
-  <si>
-    <t>Invoice</t>
-  </si>
-  <si>
-    <t>Issued</t>
-  </si>
-  <si>
-    <t>Al Rajhi bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0567878430 Yahya</t>
-  </si>
-  <si>
-    <t>C0487</t>
-  </si>
-  <si>
-    <t>Re Routed to ZAKA001 due to ZAKA013 tower will be dismental</t>
-  </si>
-  <si>
-    <t>ZAK001 Re Routed</t>
-  </si>
-  <si>
-    <t>Installation will be start tomorrow.</t>
-  </si>
-  <si>
-    <t>RIYADh</t>
-  </si>
-  <si>
-    <t>DIA-Circuit	1-274518091680</t>
-  </si>
-  <si>
-    <t>1001274526958901</t>
-  </si>
-  <si>
-    <t>Technology Equipment Trading Company	مؤسسة معدات التقانة للتجارة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Mwafaq - 0568007928 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4Mbps	</t>
-  </si>
-  <si>
-    <t>KIC-024-MW-MEL-Mobily</t>
-  </si>
-  <si>
-    <t>As per customer hold this request he will tell us once site is ready</t>
-  </si>
-  <si>
-    <t>CE1553</t>
-  </si>
-  <si>
-    <t>Installation is completed at both ends / will be delivered tomorrow.</t>
-  </si>
-  <si>
-    <t>Installtion is completed at both ends / pending due to alignment issue</t>
+    <t>KIC-024-MW-MEL-STC</t>
+  </si>
+  <si>
+    <t>KIC-025-MW-MEL-STC</t>
+  </si>
+  <si>
+    <t>KIC-026-MW-MEL-STC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Delivered </t>
   </si>
 </sst>
 </file>
@@ -732,20 +780,13 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -858,7 +899,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -915,12 +956,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
@@ -938,7 +973,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -985,19 +1020,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1027,13 +1075,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1042,57 +1084,57 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1111,181 +1153,192 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="15" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="15" fontId="15" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{83FAF997-A578-4D52-9CED-3215EBDB7938}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1727,7 +1780,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1739,7 +1792,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1938,7 +1991,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>22</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -2248,7 +2301,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>11</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>5</c:v>
@@ -2693,7 +2746,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>22</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2910,7 +2963,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -2919,7 +2972,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2</c:v>
@@ -3465,14 +3518,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="1"/>
     <col min="2" max="3" width="38.5546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="59.109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="53.5546875" style="1" customWidth="1"/>
@@ -3543,10 +3596,10 @@
         <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>17</v>
@@ -3555,709 +3608,737 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="51" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A2" s="41">
+    <row r="2" spans="1:21" s="47" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A2" s="39">
         <v>1</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="69">
+      <c r="C2" s="64">
         <v>46205</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="69">
+      <c r="K2" s="64">
         <v>46208</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="76">
+      <c r="N2" s="70">
         <v>46216</v>
       </c>
-      <c r="O2" s="76">
+      <c r="O2" s="70">
         <v>46231</v>
       </c>
-      <c r="P2" s="76">
+      <c r="P2" s="70">
         <v>46232</v>
       </c>
-      <c r="Q2" s="76">
+      <c r="Q2" s="70">
         <v>46232</v>
       </c>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="T2" s="40" t="s">
+      <c r="R2" s="42"/>
+      <c r="S2" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="T2" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="U2" s="45" t="s">
+      <c r="U2" s="43" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="51" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A3" s="40">
+    <row r="3" spans="1:21" s="47" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A3" s="38">
         <v>2</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="69">
+      <c r="C3" s="64">
         <v>46205</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="49" t="s">
+      <c r="I3" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="40" t="s">
+      <c r="J3" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="69">
+      <c r="K3" s="64">
         <v>46208</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="40" t="s">
+      <c r="M3" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="76">
+      <c r="N3" s="70">
         <v>46216</v>
       </c>
-      <c r="O3" s="76">
+      <c r="O3" s="70">
         <v>46226</v>
       </c>
-      <c r="P3" s="76">
+      <c r="P3" s="70">
         <v>46228</v>
       </c>
-      <c r="Q3" s="76">
+      <c r="Q3" s="70">
         <v>46228</v>
       </c>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="T3" s="50" t="s">
+      <c r="R3" s="42"/>
+      <c r="S3" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="U3" s="45" t="s">
+      <c r="U3" s="43" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:21" s="51" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A4" s="40">
+    <row r="4" spans="1:21" s="47" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A4" s="38">
         <v>3</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="69">
+      <c r="C4" s="64">
         <v>46211</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="40" t="s">
+      <c r="J4" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="69">
+      <c r="K4" s="64">
         <v>46212</v>
       </c>
-      <c r="L4" s="40" t="s">
+      <c r="L4" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="M4" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="76">
+      <c r="N4" s="70">
         <v>46222</v>
       </c>
-      <c r="O4" s="76">
+      <c r="O4" s="70">
         <v>46228</v>
       </c>
-      <c r="P4" s="76">
+      <c r="P4" s="70">
         <v>46229</v>
       </c>
-      <c r="Q4" s="76">
+      <c r="Q4" s="70">
         <v>46229</v>
       </c>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44" t="s">
-        <v>195</v>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42" t="s">
+        <v>192</v>
       </c>
       <c r="T4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="U4" s="45" t="s">
+      <c r="U4" s="43" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A5" s="40">
+      <c r="A5" s="38">
         <v>4</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="64">
         <v>46211</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="J5" s="40" t="s">
+      <c r="J5" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="69">
+      <c r="K5" s="64">
         <v>46216</v>
       </c>
-      <c r="L5" s="40" t="s">
+      <c r="L5" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="40" t="s">
+      <c r="M5" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="N5" s="76">
+      <c r="N5" s="70">
         <v>46230</v>
       </c>
-      <c r="O5" s="76">
+      <c r="O5" s="70">
         <v>46243</v>
       </c>
-      <c r="P5" s="76">
+      <c r="P5" s="70">
         <v>46243</v>
       </c>
-      <c r="Q5" s="76">
+      <c r="Q5" s="70">
         <v>46243</v>
       </c>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="40" t="s">
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="U5" s="45" t="s">
+      <c r="U5" s="43" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:21" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="8">
+      <c r="A6" s="38">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="71">
+      <c r="C6" s="64">
         <v>46213</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="71">
+      <c r="K6" s="64">
         <v>46216</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="78">
+      <c r="N6" s="70">
         <v>46244</v>
       </c>
-      <c r="O6" s="78"/>
-      <c r="P6" s="78"/>
-      <c r="Q6" s="78"/>
-      <c r="T6" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="U6" s="5" t="s">
+      <c r="O6" s="70">
+        <v>46246</v>
+      </c>
+      <c r="P6" s="70">
+        <v>46246</v>
+      </c>
+      <c r="Q6" s="70">
+        <v>46247</v>
+      </c>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="U6" s="43" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:21" s="5" customFormat="1" ht="13.8" customHeight="1">
-      <c r="A7" s="40">
+      <c r="A7" s="38">
         <v>6</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="69">
+      <c r="C7" s="64">
         <v>46234</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="J7" s="40" t="s">
+      <c r="J7" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="64">
         <v>46216</v>
       </c>
-      <c r="L7" s="40" t="s">
+      <c r="L7" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="40" t="s">
+      <c r="M7" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="70">
         <v>46234</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="70">
         <v>46236</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="70">
         <v>46236</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="70">
         <v>46206</v>
       </c>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="T7" s="40" t="s">
+      <c r="R7" s="42"/>
+      <c r="S7" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="T7" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="U7" s="45" t="s">
+      <c r="U7" s="43" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A8" s="8">
+      <c r="A8" s="38">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="71">
+      <c r="C8" s="64">
         <v>46215</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="K8" s="71">
+      <c r="K8" s="64">
         <v>46216</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="78"/>
-      <c r="O8" s="78"/>
-      <c r="P8" s="78"/>
-      <c r="Q8" s="78"/>
-      <c r="T8" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" s="51" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A9" s="40">
+      <c r="N8" s="70">
+        <v>46234</v>
+      </c>
+      <c r="O8" s="70">
+        <v>46237</v>
+      </c>
+      <c r="P8" s="70">
+        <v>46238</v>
+      </c>
+      <c r="Q8" s="70">
+        <v>46239</v>
+      </c>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="U8" s="43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" s="47" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A9" s="38">
         <v>8</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="69">
+      <c r="C9" s="64">
         <v>46224</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="G9" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="H9" s="40" t="s">
+      <c r="G9" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="H9" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="J9" s="40" t="s">
+      <c r="J9" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="K9" s="69">
+      <c r="K9" s="64">
         <v>46224</v>
       </c>
-      <c r="L9" s="40" t="s">
+      <c r="L9" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M9" s="40" t="s">
+      <c r="M9" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="N9" s="76">
+      <c r="N9" s="70">
         <v>46226</v>
       </c>
-      <c r="O9" s="76">
+      <c r="O9" s="70">
         <v>46226</v>
       </c>
-      <c r="P9" s="76">
+      <c r="P9" s="70">
         <v>46226</v>
       </c>
-      <c r="Q9" s="76">
+      <c r="Q9" s="70">
         <v>46237</v>
       </c>
-      <c r="R9" s="44" t="s">
+      <c r="R9" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="S9" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="S9" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="T9" s="60" t="s">
+      <c r="T9" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="U9" s="45" t="s">
+      <c r="U9" s="43" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A10" s="8">
+      <c r="A10" s="48">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="71">
+      <c r="C10" s="65">
         <v>46219</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="H10" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="I10" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="J10" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="71">
+      <c r="K10" s="65">
+        <v>46238</v>
+      </c>
+      <c r="L10" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="N10" s="71">
+        <v>46234</v>
+      </c>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="U10" s="53" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" s="47" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A11" s="38">
+        <v>10</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="64">
+        <v>46216</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="64">
+        <v>46216</v>
+      </c>
+      <c r="L11" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="N11" s="70">
+        <v>46219</v>
+      </c>
+      <c r="O11" s="70">
         <v>46223</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="P11" s="70">
+        <v>46223</v>
+      </c>
+      <c r="Q11" s="70">
+        <v>46223</v>
+      </c>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="U11" s="43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A12" s="48">
+        <v>11</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="65">
+        <v>46216</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="65">
+        <v>46216</v>
+      </c>
+      <c r="L12" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="N10" s="78"/>
-      <c r="O10" s="78"/>
-      <c r="P10" s="78"/>
-      <c r="Q10" s="78"/>
-      <c r="T10" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" s="51" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A11" s="40">
-        <v>10</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="69">
+      <c r="M12" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="N12" s="71">
+        <v>46219</v>
+      </c>
+      <c r="O12" s="71">
+        <v>46226</v>
+      </c>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="52"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="U12" s="53" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="47" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A13" s="38">
+        <v>12</v>
+      </c>
+      <c r="B13" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="67">
         <v>46216</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D13" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" s="40" t="s">
+      <c r="E13" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="I11" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="J11" s="40" t="s">
+      <c r="I13" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="J13" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="69">
+      <c r="K13" s="67">
         <v>46216</v>
       </c>
-      <c r="L11" s="40" t="s">
+      <c r="L13" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="M11" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="N11" s="76">
+      <c r="M13" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="N13" s="73">
         <v>46219</v>
       </c>
-      <c r="O11" s="76">
+      <c r="O13" s="73">
+        <v>46220</v>
+      </c>
+      <c r="P13" s="73">
         <v>46223</v>
       </c>
-      <c r="P11" s="76">
-        <v>46223</v>
-      </c>
-      <c r="Q11" s="76">
-        <v>46223</v>
-      </c>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="50" t="s">
+      <c r="Q13" s="73">
+        <v>46227</v>
+      </c>
+      <c r="R13" s="62"/>
+      <c r="S13" s="62"/>
+      <c r="T13" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="U11" s="45" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A12" s="52">
-        <v>11</v>
-      </c>
-      <c r="B12" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="70">
-        <v>46216</v>
-      </c>
-      <c r="D12" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="55" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="I12" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="J12" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="70">
-        <v>46216</v>
-      </c>
-      <c r="L12" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="N12" s="77">
-        <v>46219</v>
-      </c>
-      <c r="O12" s="77">
-        <v>46226</v>
-      </c>
-      <c r="P12" s="77"/>
-      <c r="Q12" s="77"/>
-      <c r="R12" s="56"/>
-      <c r="S12" s="56"/>
-      <c r="T12" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="U12" s="57" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" s="51" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A13" s="40">
-        <v>12</v>
-      </c>
-      <c r="B13" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" s="72">
-        <v>46216</v>
-      </c>
-      <c r="D13" s="63" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="60" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="64" t="s">
-        <v>93</v>
-      </c>
-      <c r="G13" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="H13" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="I13" s="60" t="s">
-        <v>89</v>
-      </c>
-      <c r="J13" s="60" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" s="72">
-        <v>46216</v>
-      </c>
-      <c r="L13" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" s="60" t="s">
-        <v>95</v>
-      </c>
-      <c r="N13" s="79">
-        <v>46219</v>
-      </c>
-      <c r="O13" s="79">
-        <v>46220</v>
-      </c>
-      <c r="P13" s="79">
-        <v>46223</v>
-      </c>
-      <c r="Q13" s="79">
-        <v>46227</v>
-      </c>
-      <c r="R13" s="67"/>
-      <c r="S13" s="67"/>
-      <c r="T13" s="68" t="s">
-        <v>85</v>
-      </c>
-      <c r="U13" s="66" t="s">
+      <c r="U13" s="61" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4268,7 +4349,7 @@
       <c r="B14" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="71">
+      <c r="C14" s="66">
         <v>46177</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -4292,17 +4373,17 @@
       <c r="J14" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="K14" s="71"/>
+      <c r="K14" s="66"/>
       <c r="L14" s="8" t="s">
         <v>27</v>
       </c>
       <c r="M14" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="78"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
       <c r="T14" s="8" t="s">
         <v>29</v>
       </c>
@@ -4314,7 +4395,7 @@
       <c r="B15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="71">
+      <c r="C15" s="66">
         <v>46222</v>
       </c>
       <c r="D15" s="8" t="s">
@@ -4338,7 +4419,7 @@
       <c r="J15" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="K15" s="71">
+      <c r="K15" s="66">
         <v>46223</v>
       </c>
       <c r="L15" s="8" t="s">
@@ -4358,61 +4439,61 @@
       </c>
     </row>
     <row r="16" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A16" s="8">
+      <c r="A16" s="48">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="71">
+      <c r="C16" s="65">
         <v>46222</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="K16" s="71">
+      <c r="K16" s="65">
         <v>46223</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="M16" s="8" t="s">
+      <c r="M16" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="N16" s="78">
+      <c r="N16" s="71">
         <v>46243</v>
       </c>
-      <c r="O16" s="78">
+      <c r="O16" s="71">
         <v>46244</v>
       </c>
-      <c r="P16" s="78">
+      <c r="P16" s="71">
         <v>46245</v>
       </c>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="U16" s="5" t="s">
+      <c r="Q16" s="76"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="U16" s="53" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4423,7 +4504,7 @@
       <c r="B17" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C17" s="71">
+      <c r="C17" s="66">
         <v>46229</v>
       </c>
       <c r="D17" s="8" t="s">
@@ -4447,7 +4528,7 @@
       <c r="J17" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="K17" s="71">
+      <c r="K17" s="66">
         <v>46231</v>
       </c>
       <c r="L17" s="8" t="s">
@@ -4474,7 +4555,7 @@
       <c r="B18" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="73">
+      <c r="C18" s="68">
         <v>46229</v>
       </c>
       <c r="D18" s="8" t="s">
@@ -4492,13 +4573,13 @@
       <c r="H18" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="14" t="s">
         <v>106</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="K18" s="71">
+      <c r="K18" s="66">
         <v>46231</v>
       </c>
       <c r="L18" s="8" t="s">
@@ -4518,410 +4599,530 @@
       </c>
       <c r="U18" s="8"/>
     </row>
-    <row r="19" spans="1:21" s="51" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A19" s="40">
+    <row r="19" spans="1:21" s="47" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A19" s="38">
         <v>18</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="C19" s="69">
+      <c r="C19" s="64">
         <v>46232</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="G19" s="43" t="s">
+      <c r="G19" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="J19" s="40" t="s">
+      <c r="J19" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="K19" s="69">
+      <c r="K19" s="64">
         <v>46232</v>
       </c>
-      <c r="L19" s="40" t="s">
+      <c r="L19" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="M19" s="40" t="s">
+      <c r="M19" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="N19" s="70">
+        <v>46233</v>
+      </c>
+      <c r="O19" s="70">
+        <v>46233</v>
+      </c>
+      <c r="P19" s="70">
+        <v>46233</v>
+      </c>
+      <c r="Q19" s="70">
+        <v>46236</v>
+      </c>
+      <c r="R19" s="42"/>
+      <c r="S19" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="T19" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="U19" s="43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" s="47" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A20" s="38">
+        <v>19</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="69">
+        <v>46234</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="I20" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="K20" s="64">
+        <v>46231</v>
+      </c>
+      <c r="L20" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="N20" s="74">
+        <v>46234</v>
+      </c>
+      <c r="O20" s="70">
+        <v>46235</v>
+      </c>
+      <c r="P20" s="70">
+        <v>46236</v>
+      </c>
+      <c r="Q20" s="70">
+        <v>46236</v>
+      </c>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="T20" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="U20" s="43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A21" s="48">
+        <v>20</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="65">
+        <v>46237</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="G21" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="I21" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="J21" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="K21" s="65"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="53"/>
+      <c r="T21" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="U21" s="53" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A22" s="38">
+        <v>21</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="77">
+        <v>46244</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="F22" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="N19" s="76">
-        <v>46233</v>
-      </c>
-      <c r="O19" s="76">
-        <v>46233</v>
-      </c>
-      <c r="P19" s="76">
-        <v>46233</v>
-      </c>
-      <c r="Q19" s="76">
-        <v>46236</v>
-      </c>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="T19" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="U19" s="45" t="s">
+      <c r="G22" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="H22" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="I22" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="J22" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="K22" s="77">
+        <v>46244</v>
+      </c>
+      <c r="L22" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="N22" s="42">
+        <v>46245</v>
+      </c>
+      <c r="O22" s="42">
+        <v>46245</v>
+      </c>
+      <c r="P22" s="42">
+        <v>46245</v>
+      </c>
+      <c r="Q22" s="42">
+        <v>46246</v>
+      </c>
+      <c r="R22" s="43"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="U22" s="43" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:21" s="51" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A20" s="40">
-        <v>19</v>
-      </c>
-      <c r="B20" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="74">
-        <v>46234</v>
-      </c>
-      <c r="D20" s="48" t="s">
+    <row r="23" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A23" s="38">
+        <v>22</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="C23" s="98">
+        <v>46247</v>
+      </c>
+      <c r="D23" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="48" t="s">
+      <c r="E23" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="G20" s="48" t="s">
-        <v>176</v>
-      </c>
-      <c r="H20" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="I20" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="J20" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="K20" s="69">
-        <v>46231</v>
-      </c>
-      <c r="L20" s="40" t="s">
+      <c r="F23" s="99" t="s">
+        <v>208</v>
+      </c>
+      <c r="G23" s="99" t="s">
+        <v>220</v>
+      </c>
+      <c r="H23" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="I23" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="J23" s="99" t="s">
+        <v>216</v>
+      </c>
+      <c r="K23" s="38"/>
+      <c r="L23" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="M20" s="48" t="s">
-        <v>175</v>
-      </c>
-      <c r="N20" s="80">
-        <v>46234</v>
-      </c>
-      <c r="O20" s="76">
-        <v>46235</v>
-      </c>
-      <c r="P20" s="76">
-        <v>46236</v>
-      </c>
-      <c r="Q20" s="76">
-        <v>46236</v>
-      </c>
-      <c r="R20" s="44"/>
-      <c r="S20" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="T20" s="40" t="s">
+      <c r="M23" s="99" t="s">
+        <v>212</v>
+      </c>
+      <c r="N23" s="42">
+        <v>46247</v>
+      </c>
+      <c r="O23" s="42">
+        <v>46249</v>
+      </c>
+      <c r="P23" s="42">
+        <v>46249</v>
+      </c>
+      <c r="Q23" s="42">
+        <v>46249</v>
+      </c>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="U20" s="45" t="s">
+      <c r="U23" s="43" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A21" s="40">
+    <row r="24" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A24" s="38">
+        <v>23</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24" s="98">
+        <v>46247</v>
+      </c>
+      <c r="D24" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="40" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" s="74">
-        <v>46234</v>
-      </c>
-      <c r="D21" s="82" t="s">
+      <c r="E24" s="99" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="99" t="s">
+        <v>209</v>
+      </c>
+      <c r="G24" s="99" t="s">
+        <v>221</v>
+      </c>
+      <c r="H24" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="I24" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="J24" s="99" t="s">
+        <v>217</v>
+      </c>
+      <c r="K24" s="38"/>
+      <c r="L24" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="99" t="s">
+        <v>213</v>
+      </c>
+      <c r="N24" s="42">
+        <v>46247</v>
+      </c>
+      <c r="O24" s="42">
+        <v>46249</v>
+      </c>
+      <c r="P24" s="42">
+        <v>46249</v>
+      </c>
+      <c r="Q24" s="42">
+        <v>46249</v>
+      </c>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
+      <c r="T24" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="U24" s="43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A25" s="38">
+        <v>24</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="C25" s="98">
+        <v>46247</v>
+      </c>
+      <c r="D25" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="82" t="s">
+      <c r="E25" s="100" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21" s="82" t="s">
-        <v>67</v>
-      </c>
-      <c r="H21" s="82" t="s">
-        <v>178</v>
-      </c>
-      <c r="I21" s="82" t="s">
-        <v>179</v>
-      </c>
-      <c r="J21" s="82" t="s">
-        <v>180</v>
-      </c>
-      <c r="K21" s="69">
-        <v>46216</v>
-      </c>
-      <c r="L21" s="40" t="s">
+      <c r="F25" s="99" t="s">
+        <v>210</v>
+      </c>
+      <c r="G25" s="100" t="s">
+        <v>222</v>
+      </c>
+      <c r="H25" s="100" t="s">
+        <v>218</v>
+      </c>
+      <c r="I25" s="100" t="s">
+        <v>219</v>
+      </c>
+      <c r="J25" s="100" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="38"/>
+      <c r="L25" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="M21" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="N21" s="80">
-        <v>46234</v>
-      </c>
-      <c r="O21" s="76">
-        <v>46237</v>
-      </c>
-      <c r="P21" s="76">
-        <v>46238</v>
-      </c>
-      <c r="Q21" s="76">
-        <v>46239</v>
-      </c>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="U21" s="45" t="s">
+      <c r="M25" s="99" t="s">
+        <v>214</v>
+      </c>
+      <c r="N25" s="42">
+        <v>46247</v>
+      </c>
+      <c r="O25" s="42">
+        <v>46248</v>
+      </c>
+      <c r="P25" s="42">
+        <v>46248</v>
+      </c>
+      <c r="Q25" s="42">
+        <v>46249</v>
+      </c>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="U25" s="43" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A22" s="8">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C22" s="75">
-        <v>46234</v>
-      </c>
-      <c r="D22" s="46" t="s">
+    <row r="26" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A26" s="38">
+        <v>25</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="C26" s="98">
+        <v>46247</v>
+      </c>
+      <c r="D26" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="46" t="s">
+      <c r="E26" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="G22" s="46" t="s">
-        <v>177</v>
-      </c>
-      <c r="H22" s="61" t="s">
-        <v>196</v>
-      </c>
-      <c r="I22" s="61" t="s">
-        <v>197</v>
-      </c>
-      <c r="J22" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="K22" s="71">
-        <v>46238</v>
-      </c>
-      <c r="L22" s="8" t="s">
+      <c r="F26" s="99" t="s">
+        <v>211</v>
+      </c>
+      <c r="G26" s="99" t="s">
+        <v>223</v>
+      </c>
+      <c r="H26" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="I26" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="J26" s="99" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="38"/>
+      <c r="L26" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="M22" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="N22" s="81">
-        <v>46234</v>
-      </c>
-      <c r="O22" s="78"/>
-      <c r="P22" s="78"/>
-      <c r="Q22" s="78"/>
-      <c r="T22" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="U22" s="5" t="s">
+      <c r="M26" s="99" t="s">
+        <v>215</v>
+      </c>
+      <c r="N26" s="42">
+        <v>46247</v>
+      </c>
+      <c r="O26" s="42">
+        <v>46248</v>
+      </c>
+      <c r="P26" s="42">
+        <v>46248</v>
+      </c>
+      <c r="Q26" s="42">
+        <v>46249</v>
+      </c>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="U26" s="43" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A23" s="8">
-        <v>22</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C23" s="71">
-        <v>46237</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="K23" s="71"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="N23" s="78"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
-      <c r="T23" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="U23" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A24" s="8">
-        <v>23</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="C24" s="12">
-        <v>46244</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="K24" s="12">
-        <v>46244</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="N24" s="102">
-        <v>46245</v>
-      </c>
-      <c r="O24" s="102">
-        <v>46245</v>
-      </c>
-      <c r="P24" s="102">
-        <v>46245</v>
-      </c>
-      <c r="T24" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="U24" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G25" s="17"/>
-    </row>
-    <row r="26" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G26" s="17"/>
-    </row>
     <row r="27" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G27" s="17"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G28" s="17"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G29" s="17"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G30" s="17"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G31" s="17"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" spans="1:21" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G32" s="17"/>
+      <c r="G32" s="15"/>
     </row>
     <row r="33" spans="7:7" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G33" s="17"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" spans="7:7" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G34" s="17"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="7:7" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G35" s="17"/>
+      <c r="G35" s="15"/>
     </row>
     <row r="36" spans="7:7" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G36" s="17"/>
+      <c r="G36" s="15"/>
     </row>
     <row r="37" spans="7:7" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G37" s="17"/>
+      <c r="G37" s="15"/>
     </row>
     <row r="38" spans="7:7" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G38" s="17"/>
+      <c r="G38" s="15"/>
     </row>
     <row r="39" spans="7:7" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G39" s="17"/>
+      <c r="G39" s="15"/>
     </row>
     <row r="40" spans="7:7" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G40" s="17"/>
-    </row>
-    <row r="41" spans="7:7" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G41" s="17"/>
-    </row>
-    <row r="42" spans="7:7" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="G42" s="17"/>
+      <c r="G40" s="15"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="F2:F22">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R23" xr:uid="{BC98B305-C019-4985-95C5-513356380383}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R21" xr:uid="{BC98B305-C019-4985-95C5-513356380383}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S23" xr:uid="{C06E9C4F-A2EF-4FFA-B671-F3ABC2D50D56}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S21" xr:uid="{C06E9C4F-A2EF-4FFA-B671-F3ABC2D50D56}">
       <formula1>"Issued,Pending"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4953,61 +5154,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="14.25" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="16" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5051,7 +5252,7 @@
       <c r="M2" s="12">
         <v>46223</v>
       </c>
-      <c r="R2" s="19" t="s">
+      <c r="R2" s="17" t="s">
         <v>126</v>
       </c>
     </row>
@@ -5088,593 +5289,593 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="19.5" customHeight="1">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
     </row>
     <row r="2" spans="1:17" ht="19.5" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
     </row>
     <row r="3" spans="1:17" ht="14.25" customHeight="1">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="91" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
     </row>
     <row r="5" spans="1:17" ht="27.75" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="92" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97" t="s">
+      <c r="B5" s="92"/>
+      <c r="C5" s="93" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="97"/>
-      <c r="E5" s="98" t="s">
+      <c r="D5" s="93"/>
+      <c r="E5" s="94" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="98"/>
-      <c r="G5" s="99" t="s">
+      <c r="F5" s="94"/>
+      <c r="G5" s="95" t="s">
         <v>131</v>
       </c>
-      <c r="H5" s="99"/>
-      <c r="I5" s="100" t="s">
+      <c r="H5" s="95"/>
+      <c r="I5" s="96" t="s">
         <v>132</v>
       </c>
-      <c r="J5" s="100"/>
-      <c r="K5" s="101" t="s">
+      <c r="J5" s="96"/>
+      <c r="K5" s="97" t="s">
         <v>133</v>
       </c>
-      <c r="L5" s="101"/>
-      <c r="M5" s="86" t="s">
+      <c r="L5" s="97"/>
+      <c r="M5" s="82" t="s">
         <v>134</v>
       </c>
-      <c r="N5" s="86"/>
-      <c r="O5" s="87" t="s">
+      <c r="N5" s="82"/>
+      <c r="O5" s="83" t="s">
         <v>135</v>
       </c>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="20"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="18"/>
     </row>
     <row r="6" spans="1:17" ht="21.75" customHeight="1">
-      <c r="A6" s="88">
-        <f>COUNTA('Active Orders'!$A$2:$A$499)</f>
-        <v>23</v>
-      </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="89">
-        <f>COUNTIF('Active Orders'!$L$2:$L$499,"CLOS")</f>
-        <v>22</v>
-      </c>
-      <c r="D6" s="89"/>
-      <c r="E6" s="90">
-        <f>COUNTIF('Active Orders'!$T$2:$T$499,"In Process")+COUNTIF('Active Orders'!$T$2:$T$499,"Under MW Installation")+COUNTIF('Active Orders'!$T$2:$T$499,"Under MW Installation- Brown Condition")</f>
+      <c r="A6" s="84">
+        <f>COUNTA('Active Orders'!$A$2:$A$497)</f>
+        <v>25</v>
+      </c>
+      <c r="B6" s="84"/>
+      <c r="C6" s="85">
+        <f>COUNTIF('Active Orders'!$L$2:$L$497,"CLOS")</f>
+        <v>24</v>
+      </c>
+      <c r="D6" s="85"/>
+      <c r="E6" s="86">
+        <f>COUNTIF('Active Orders'!$T$2:$T$497,"In Process")+COUNTIF('Active Orders'!$T$2:$T$497,"Under MW Installation")+COUNTIF('Active Orders'!$T$2:$T$497,"Under MW Installation- Brown Condition")</f>
         <v>1</v>
       </c>
-      <c r="F6" s="90"/>
-      <c r="G6" s="91">
-        <f>COUNTIF('Active Orders'!$T$2:$T$499,"Under TWAL Approval")</f>
+      <c r="F6" s="86"/>
+      <c r="G6" s="87">
+        <f>COUNTIF('Active Orders'!$T$2:$T$497,"Under TWAL Approval")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="91"/>
-      <c r="I6" s="92">
-        <f>COUNTIFS('Active Orders'!$A$2:$A$499,"&lt;&gt;",'Active Orders'!$T$2:$T$499,"")</f>
+      <c r="H6" s="87"/>
+      <c r="I6" s="88">
+        <f>COUNTIFS('Active Orders'!$A$2:$A$497,"&lt;&gt;",'Active Orders'!$T$2:$T$497,"")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="92"/>
-      <c r="K6" s="91">
+      <c r="J6" s="88"/>
+      <c r="K6" s="87">
         <f>COUNTA('Cancelled Orders'!$B$2:$B$500)</f>
         <v>1</v>
       </c>
-      <c r="L6" s="91"/>
-      <c r="M6" s="93">
-        <f>COUNTIF('Active Orders'!$T$2:$T$499,"Delivered*")</f>
-        <v>11</v>
-      </c>
-      <c r="N6" s="93"/>
-      <c r="O6" s="88">
+      <c r="L6" s="87"/>
+      <c r="M6" s="89">
+        <f>COUNTIF('Active Orders'!$T$2:$T$497,"Delivered*")</f>
+        <v>16</v>
+      </c>
+      <c r="N6" s="89"/>
+      <c r="O6" s="84">
         <f>A6+K6</f>
+        <v>26</v>
+      </c>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="19"/>
+    </row>
+    <row r="7" spans="1:17" ht="21.75" customHeight="1">
+      <c r="A7" s="84"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="88"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="89"/>
+      <c r="N7" s="89"/>
+      <c r="O7" s="84"/>
+      <c r="P7" s="84"/>
+    </row>
+    <row r="9" spans="1:17" ht="18" customHeight="1">
+      <c r="A9" s="79" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="79"/>
+      <c r="C9" s="79"/>
+      <c r="E9" s="79" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="79"/>
+    </row>
+    <row r="10" spans="1:17" ht="14.25" customHeight="1">
+      <c r="A10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="14.25" customHeight="1">
+      <c r="A11" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="22">
+        <f>COUNTIF('Active Orders'!$T$2:$T$497,"Under Activation")</f>
+        <v>3</v>
+      </c>
+      <c r="C11" s="23">
+        <f>B11/$B$16</f>
+        <v>0.15</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="22">
+        <f>COUNTIF('Active Orders'!$D$2:$D$497,"CENTRAL")</f>
         <v>24</v>
       </c>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="21"/>
-    </row>
-    <row r="7" spans="1:17" ht="21.75" customHeight="1">
-      <c r="A7" s="88"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="90"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="88"/>
-      <c r="P7" s="88"/>
-    </row>
-    <row r="9" spans="1:17" ht="18" customHeight="1">
-      <c r="A9" s="83" t="s">
-        <v>136</v>
-      </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="E9" s="83" t="s">
-        <v>137</v>
-      </c>
-      <c r="F9" s="83"/>
-    </row>
-    <row r="10" spans="1:17" ht="14.25" customHeight="1">
-      <c r="A10" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="14.25" customHeight="1">
-      <c r="A11" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="24">
-        <f>COUNTIF('Active Orders'!$T$2:$T$499,"Under Activation")</f>
-        <v>5</v>
-      </c>
-      <c r="C11" s="25">
-        <f>B11/$B$16</f>
-        <v>0.29411764705882354</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="24">
-        <f>COUNTIF('Active Orders'!$D$2:$D$499,"CENTRAL")</f>
-        <v>22</v>
-      </c>
     </row>
     <row r="12" spans="1:17" ht="14.25" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="24">
-        <f>COUNTIF('Active Orders'!$T$2:$T$499,"Under TWAL Approval")</f>
+      <c r="B12" s="22">
+        <f>COUNTIF('Active Orders'!$T$2:$T$497,"Under TWAL Approval")</f>
         <v>0</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="23">
         <f>B12/$B$16</f>
         <v>0</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="24">
-        <f>COUNTIF('Active Orders'!$D$2:$D$499,"EAST")</f>
+      <c r="F12" s="22">
+        <f>COUNTIF('Active Orders'!$D$2:$D$497,"EAST")</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="14.25" customHeight="1">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="24">
-        <f>COUNTIF('Active Orders'!$T$2:$T$499,"Under MW Installation")</f>
+      <c r="B13" s="22">
+        <f>COUNTIF('Active Orders'!$T$2:$T$497,"Under MW Installation")</f>
         <v>1</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="23">
         <f>B13/$B$16</f>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="E13" s="23" t="s">
+        <v>0.05</v>
+      </c>
+      <c r="E13" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="F13" s="24">
-        <f>COUNTIFS('Active Orders'!$A$2:$A$499,"&lt;&gt;",'Active Orders'!$D$2:$D$499,"")</f>
+      <c r="F13" s="22">
+        <f>COUNTIFS('Active Orders'!$A$2:$A$497,"&lt;&gt;",'Active Orders'!$D$2:$D$497,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="14.25" customHeight="1">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="24">
-        <f>COUNTIFS('Active Orders'!$A$2:$A$499,"&lt;&gt;",'Active Orders'!$T$2:$T$499,"")</f>
+      <c r="B14" s="22">
+        <f>COUNTIFS('Active Orders'!$A$2:$A$497,"&lt;&gt;",'Active Orders'!$T$2:$T$497,"")</f>
         <v>0</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="23">
         <f>B14/$B$16</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="24">
-        <f>COUNTIF('Active Orders'!$T$2:$T$499,"Delivered*")</f>
-        <v>11</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="B15" s="22">
+        <f>COUNTIF('Active Orders'!$T$2:$T$497,"Delivered*")</f>
+        <v>16</v>
+      </c>
+      <c r="C15" s="23">
         <f>B15/$B$16</f>
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="E15" s="83" t="s">
+        <v>0.8</v>
+      </c>
+      <c r="E15" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="F15" s="83"/>
+      <c r="F15" s="79"/>
     </row>
     <row r="16" spans="1:17" ht="14.25" customHeight="1">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="25">
         <f>SUM(B11:B15)</f>
-        <v>17</v>
-      </c>
-      <c r="C16" s="28">
+        <v>20</v>
+      </c>
+      <c r="C16" s="26">
         <f>SUM(C11:C15)</f>
         <v>1</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="20" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A17" s="29"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="E17" s="23" t="s">
+      <c r="A17" s="27"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="E17" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="22">
         <f>COUNTA('Cancelled Orders'!$B$2:$B$500)</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A18" s="32"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="34"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="32"/>
     </row>
     <row r="20" spans="1:6" ht="17.25" customHeight="1">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="79" t="s">
         <v>147</v>
       </c>
-      <c r="B20" s="83"/>
-      <c r="E20" s="83" t="s">
+      <c r="B20" s="79"/>
+      <c r="E20" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="F20" s="83"/>
+      <c r="F20" s="79"/>
     </row>
     <row r="21" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="20" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="24">
-        <f>COUNTIF('Active Orders'!$E$2:$E$499,"RIYADHDST")</f>
-        <v>11</v>
-      </c>
-      <c r="E22" s="23" t="s">
+      <c r="B22" s="22">
+        <f>COUNTIF('Active Orders'!$E$2:$E$497,"RIYADHDST")</f>
+        <v>13</v>
+      </c>
+      <c r="E22" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="24">
-        <f>COUNTIF('Active Orders'!$L$2:$L$499,"CLOS")</f>
+      <c r="F22" s="22">
+        <f>COUNTIF('Active Orders'!$L$2:$L$497,"CLOS")</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A23" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="22">
+        <f>COUNTIF('Active Orders'!$E$2:$E$497,"QASSIM")</f>
+        <v>5</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="22">
+        <f>COUNTIF('Active Orders'!$L$2:$L$497,"Pending")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A24" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="22">
+        <f>COUNTIF('Active Orders'!$E$2:$E$497,"RIYADH")</f>
+        <v>5</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" s="22">
+        <f>COUNTIFS('Active Orders'!$A$2:$A$497,"&lt;&gt;",'Active Orders'!$L$2:$L$497,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="22">
+        <f>COUNTIF('Active Orders'!$E$2:$E$497,"ALAHSA")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A26" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="22">
+        <f>COUNTIFS('Active Orders'!$A$2:$A$497,"&lt;&gt;",'Active Orders'!$E$2:$E$497,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="17.25" customHeight="1">
+      <c r="A29" s="79" t="s">
+        <v>151</v>
+      </c>
+      <c r="B29" s="79"/>
+    </row>
+    <row r="30" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A30" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A31" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="22">
+        <f>COUNTIF('Active Orders'!$J$2:$J$497,"100Mbps")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A32" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="22">
+        <f>COUNTIF('Active Orders'!$J$2:$J$497,"25MBPs")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A33" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="22">
+        <f>COUNTIF('Active Orders'!$J$2:$J$497,"20MBPs")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A34" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="22">
+        <f>COUNTIF('Active Orders'!$J$2:$J$497,"8MBPs")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A35" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="22">
+        <f>COUNTIF('Active Orders'!$J$2:$J$497,"6MBPs")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A36" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="22">
+        <f>COUNTIF('Active Orders'!$J$2:$J$497,"4MBPs")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A37" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B37" s="22">
+        <f>COUNTIFS('Active Orders'!$A$2:$A$497,"&lt;&gt;",'Active Orders'!$J$2:$J$497,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A40" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="80"/>
+      <c r="C40" s="80"/>
+    </row>
+    <row r="41" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A41" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A42" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="35">
+        <f>COUNTIF('Active Orders'!$B$2:$B$497,"*STC")</f>
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A23" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="24">
-        <f>COUNTIF('Active Orders'!$E$2:$E$499,"QASSIM")</f>
-        <v>5</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="F23" s="24">
-        <f>COUNTIF('Active Orders'!$L$2:$L$499,"Pending")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A24" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="24">
-        <f>COUNTIF('Active Orders'!$E$2:$E$499,"RIYADH")</f>
-        <v>5</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="F24" s="24">
-        <f>COUNTIFS('Active Orders'!$A$2:$A$499,"&lt;&gt;",'Active Orders'!$L$2:$L$499,"")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A25" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" s="24">
-        <f>COUNTIF('Active Orders'!$E$2:$E$499,"ALAHSA")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A26" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="24">
-        <f>COUNTIFS('Active Orders'!$A$2:$A$499,"&lt;&gt;",'Active Orders'!$E$2:$E$499,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1">
-      <c r="A29" s="83" t="s">
-        <v>151</v>
-      </c>
-      <c r="B29" s="83"/>
-    </row>
-    <row r="30" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A30" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A31" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="24">
-        <f>COUNTIF('Active Orders'!$J$2:$J$499,"100Mbps")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A32" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="24">
-        <f>COUNTIF('Active Orders'!$J$2:$J$499,"25MBPs")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A33" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="24">
-        <f>COUNTIF('Active Orders'!$J$2:$J$499,"20MBPs")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A34" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="24">
-        <f>COUNTIF('Active Orders'!$J$2:$J$499,"8MBPs")</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A35" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="24">
-        <f>COUNTIF('Active Orders'!$J$2:$J$499,"6MBPs")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A36" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="24">
-        <f>COUNTIF('Active Orders'!$J$2:$J$499,"4MBPs")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A37" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="B37" s="24">
-        <f>COUNTIFS('Active Orders'!$A$2:$A$499,"&lt;&gt;",'Active Orders'!$J$2:$J$499,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A40" s="84" t="s">
-        <v>153</v>
-      </c>
-      <c r="B40" s="84"/>
-      <c r="C40" s="84"/>
-    </row>
-    <row r="41" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A41" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="C41" s="35" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A42" s="36" t="s">
+    <row r="43" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A43" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="B42" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="C42" s="37">
-        <f>COUNTIF('Active Orders'!$B$2:$B$499,"*STC")</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A43" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="B43" s="36" t="s">
+      <c r="B43" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="C43" s="37">
+      <c r="C43" s="35">
         <f>COUNTIF('Cancelled Orders'!$B$2:$B$500,"*STC")</f>
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="B44" s="36" t="s">
+      <c r="B44" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="C44" s="37">
-        <f>COUNTIF('Active Orders'!$B$2:$B$499,"*Mobily")</f>
+      <c r="C44" s="35">
+        <f>COUNTIF('Active Orders'!$B$2:$B$497,"*Mobily")</f>
         <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A45" s="36" t="s">
+      <c r="A45" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="B45" s="36" t="s">
+      <c r="B45" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="C45" s="37">
+      <c r="C45" s="35">
         <f>COUNTIF('Cancelled Orders'!$B$2:$B$500,"*Mobily")</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A46" s="85" t="s">
+      <c r="A46" s="81" t="s">
         <v>160</v>
       </c>
-      <c r="B46" s="85"/>
-      <c r="C46" s="39">
+      <c r="B46" s="81"/>
+      <c r="C46" s="37">
         <f>SUM(C42:C43)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A47" s="85" t="s">
+      <c r="A47" s="81" t="s">
         <v>161</v>
       </c>
-      <c r="B47" s="85"/>
-      <c r="C47" s="39">
+      <c r="B47" s="81"/>
+      <c r="C47" s="37">
         <f>SUM(C44:C45)</f>
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A49" s="84" t="s">
+      <c r="A49" s="80" t="s">
         <v>162</v>
       </c>
-      <c r="B49" s="84"/>
+      <c r="B49" s="80"/>
     </row>
     <row r="50" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A50" s="35" t="s">
+      <c r="A50" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="33" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="B51" s="37">
-        <f>COUNTA('Active Orders'!$B$2:$B$499)</f>
-        <v>23</v>
+      <c r="B51" s="35">
+        <f>COUNTA('Active Orders'!$B$2:$B$497)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="B52" s="37">
+      <c r="B52" s="35">
         <f>COUNTA('Cancelled Orders'!$B$2:$B$500)</f>
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A53" s="38" t="s">
+      <c r="A53" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="B53" s="39">
+      <c r="B53" s="37">
         <f>B51+B52</f>
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
